--- a/files/SSN_upcoming_projections.xlsx
+++ b/files/SSN_upcoming_projections.xlsx
@@ -65,34 +65,34 @@
     <t xml:space="preserve">1H</t>
   </si>
   <si>
+    <t xml:space="preserve">Melbourne Mavericks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queensland Firebirds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunshine Coast Lightning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adelaide Thunderbirds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GWS Giants</t>
+  </si>
+  <si>
     <t xml:space="preserve">NSW Swifts</t>
   </si>
   <si>
-    <t xml:space="preserve">Adelaide Thunderbirds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queensland Firebirds</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunshine Coast Lightning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GWS Giants</t>
+    <t xml:space="preserve">Melbourne Vixens</t>
   </si>
   <si>
     <t xml:space="preserve">West Coast Fever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melbourne Vixens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melbourne Mavericks</t>
   </si>
 </sst>
 </file>
@@ -429,8 +429,8 @@
   <cols>
     <col min="1" max="1" width="11.2056266178838" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="15.8703495591654" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="20.7099996107452" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="24.7099995328942" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="24.7099995328942" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="21.7099995912824" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.704168823845" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="15.8703495591654" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="20.5350725004471" hidden="0" customWidth="1"/>
@@ -497,7 +497,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -509,45 +509,45 @@
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7</v>
+        <v>-4.9</v>
       </c>
       <c r="F2" t="n">
-        <v>61.12</v>
+        <v>61.3</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H2" t="n">
-        <v>6.48</v>
+        <v>-4.66</v>
       </c>
       <c r="I2" t="n">
-        <v>60.01</v>
+        <v>60.52</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.31</v>
+        <v>0.9</v>
       </c>
       <c r="L2" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07</v>
+        <v>0.22</v>
       </c>
       <c r="O2" t="n">
-        <v>6.61</v>
+        <v>-4.95</v>
       </c>
       <c r="P2" t="n">
-        <v>61.19</v>
+        <v>61.52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -559,45 +559,45 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>2.81</v>
+        <v>-2.07</v>
       </c>
       <c r="F3" t="n">
-        <v>30.92</v>
+        <v>30.99</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H3" t="n">
-        <v>2.72</v>
+        <v>-1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>30.35</v>
+        <v>30.6</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.31</v>
+        <v>0.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="N3" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="O3" t="n">
-        <v>2.76</v>
+        <v>-2.1</v>
       </c>
       <c r="P3" t="n">
-        <v>30.95</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -609,45 +609,45 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>13.02</v>
+        <v>-9.52</v>
       </c>
       <c r="F4" t="n">
-        <v>121.34</v>
+        <v>121.71</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H4" t="n">
-        <v>12.59</v>
+        <v>-9.05</v>
       </c>
       <c r="I4" t="n">
-        <v>119.14</v>
+        <v>120.17</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.31</v>
+        <v>0.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.18</v>
+        <v>-0.11</v>
       </c>
       <c r="N4" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="O4" t="n">
-        <v>12.84</v>
+        <v>-9.63</v>
       </c>
       <c r="P4" t="n">
-        <v>121.47</v>
+        <v>122.15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B5" t="s">
         <v>16</v>
@@ -659,45 +659,45 @@
         <v>22</v>
       </c>
       <c r="E5" t="n">
-        <v>2.84</v>
+        <v>5.88</v>
       </c>
       <c r="F5" t="n">
-        <v>66.65</v>
+        <v>57.75</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H5" t="n">
-        <v>2.65</v>
+        <v>5.97</v>
       </c>
       <c r="I5" t="n">
-        <v>65.2</v>
+        <v>57.75</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.33</v>
+        <v>0.79</v>
       </c>
       <c r="L5" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M5" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="N5" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.98</v>
+        <v>5.97</v>
       </c>
       <c r="P5" t="n">
-        <v>66.79</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
@@ -709,45 +709,45 @@
         <v>22</v>
       </c>
       <c r="E6" t="n">
-        <v>1.19</v>
+        <v>2.49</v>
       </c>
       <c r="F6" t="n">
-        <v>33.71</v>
+        <v>29.2</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H6" t="n">
-        <v>1.11</v>
+        <v>2.53</v>
       </c>
       <c r="I6" t="n">
-        <v>32.98</v>
+        <v>29.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.33</v>
+        <v>0.79</v>
       </c>
       <c r="L6" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M6" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0.07</v>
+        <v>-0.02</v>
       </c>
       <c r="O6" t="n">
-        <v>1.26</v>
+        <v>2.53</v>
       </c>
       <c r="P6" t="n">
-        <v>33.78</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -759,45 +759,45 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>5.51</v>
+        <v>11.44</v>
       </c>
       <c r="F7" t="n">
-        <v>132.31</v>
+        <v>114.66</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H7" t="n">
-        <v>5.14</v>
+        <v>11.61</v>
       </c>
       <c r="I7" t="n">
-        <v>129.43</v>
+        <v>114.65</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.33</v>
+        <v>0.79</v>
       </c>
       <c r="L7" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M7" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="O7" t="n">
-        <v>5.8</v>
+        <v>11.61</v>
       </c>
       <c r="P7" t="n">
-        <v>132.6</v>
+        <v>114.56</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -809,45 +809,45 @@
         <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>6.69</v>
+        <v>4.48</v>
       </c>
       <c r="F8" t="n">
-        <v>60.5</v>
+        <v>65.44</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H8" t="n">
-        <v>7.04</v>
+        <v>4.33</v>
       </c>
       <c r="I8" t="n">
-        <v>60.04</v>
+        <v>65.89</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.31</v>
+        <v>0.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.16</v>
+        <v>0.01</v>
       </c>
       <c r="O8" t="n">
-        <v>6.78</v>
+        <v>4.31</v>
       </c>
       <c r="P8" t="n">
-        <v>60.33</v>
+        <v>65.45</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -859,45 +859,45 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>2.81</v>
+        <v>1.89</v>
       </c>
       <c r="F9" t="n">
-        <v>30.6</v>
+        <v>33.08</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H9" t="n">
-        <v>2.95</v>
+        <v>1.83</v>
       </c>
       <c r="I9" t="n">
-        <v>30.37</v>
+        <v>33.31</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.31</v>
+        <v>0.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M9" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="O9" t="n">
-        <v>2.85</v>
+        <v>1.81</v>
       </c>
       <c r="P9" t="n">
-        <v>30.52</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B10" t="s">
         <v>20</v>
@@ -909,45 +909,45 @@
         <v>24</v>
       </c>
       <c r="E10" t="n">
-        <v>13.01</v>
+        <v>8.7</v>
       </c>
       <c r="F10" t="n">
-        <v>120.1</v>
+        <v>129.92</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H10" t="n">
-        <v>13.68</v>
+        <v>8.42</v>
       </c>
       <c r="I10" t="n">
-        <v>119.2</v>
+        <v>130.83</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.31</v>
+        <v>0.9</v>
       </c>
       <c r="L10" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M10" t="n">
-        <v>0.18</v>
+        <v>-0.33</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.32</v>
+        <v>0.03</v>
       </c>
       <c r="O10" t="n">
-        <v>13.19</v>
+        <v>8.37</v>
       </c>
       <c r="P10" t="n">
-        <v>119.77</v>
+        <v>129.95</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
@@ -959,45 +959,45 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.77</v>
+        <v>-0.87</v>
       </c>
       <c r="F11" t="n">
-        <v>55.41</v>
+        <v>58.01</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H11" t="n">
         <v>-0.88</v>
       </c>
       <c r="I11" t="n">
-        <v>57.24</v>
+        <v>58.27</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.31</v>
+        <v>0.81</v>
       </c>
       <c r="L11" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M11" t="n">
-        <v>0.22</v>
+        <v>-0.01</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.55</v>
+        <v>-0.88</v>
       </c>
       <c r="P11" t="n">
-        <v>55.06</v>
+        <v>57.93</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
@@ -1009,45 +1009,45 @@
         <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.32</v>
+        <v>-0.37</v>
       </c>
       <c r="F12" t="n">
-        <v>28.03</v>
+        <v>29.33</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H12" t="n">
         <v>-0.37</v>
       </c>
       <c r="I12" t="n">
-        <v>28.95</v>
+        <v>29.46</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.31</v>
+        <v>0.81</v>
       </c>
       <c r="L12" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M12" t="n">
-        <v>0.11</v>
+        <v>-0.01</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.17</v>
+        <v>-0.04</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.21</v>
+        <v>-0.37</v>
       </c>
       <c r="P12" t="n">
-        <v>27.85</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46180</v>
+        <v>46187</v>
       </c>
       <c r="B13" t="s">
         <v>20</v>
@@ -1059,40 +1059,40 @@
         <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.49</v>
+        <v>-1.69</v>
       </c>
       <c r="F13" t="n">
-        <v>110</v>
+        <v>115.18</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.21</v>
+        <v>-0.19</v>
       </c>
       <c r="H13" t="n">
         <v>-1.72</v>
       </c>
       <c r="I13" t="n">
-        <v>113.64</v>
+        <v>115.7</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.31</v>
+        <v>0.81</v>
       </c>
       <c r="L13" t="n">
-        <v>0.35</v>
+        <v>0.89</v>
       </c>
       <c r="M13" t="n">
-        <v>0.44</v>
+        <v>-0.03</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.69</v>
+        <v>-0.16</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.05</v>
+        <v>-1.71</v>
       </c>
       <c r="P13" t="n">
-        <v>109.31</v>
+        <v>115.03</v>
       </c>
     </row>
   </sheetData>

--- a/files/SSN_upcoming_projections.xlsx
+++ b/files/SSN_upcoming_projections.xlsx
@@ -6,13 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="SSN Projections" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SSN PaceEff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">game_date</t>
   </si>
@@ -26,49 +26,55 @@
     <t xml:space="preserve">away_team</t>
   </si>
   <si>
-    <t xml:space="preserve">line_currentpar_overlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_currentpar_overlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h2h_home_currentpar_overlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h2h_away_currentpar_overlay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">line_team_ratings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_team_ratings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">line_currentpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total_currentpar</t>
+    <t xml:space="preserve">line_paceeff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_paceeff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_adj_paceeff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">line_scorereg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_scorereg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_adj_scorereg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_paceeff_points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hga_scorereg_points</t>
+  </si>
+  <si>
+    <t xml:space="preserve">currentpar_lineup_line_adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">currentpar_lineup_total_adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">line_paceeff_currentpar_overlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_paceeff_currentpar_overlay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melbourne Vixens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Coast Fever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1Q</t>
   </si>
   <si>
     <t xml:space="preserve">FT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adelaide Thunderbirds W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melbourne Vixens W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Coast Fever W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melbourne Maverick W</t>
   </si>
 </sst>
 </file>
@@ -76,11 +82,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -106,7 +118,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,18 +409,22 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="9.70999982483533" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="13.7099997469844" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="23.709999552357" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="20.7099996107452" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="23.709999552357" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="24.7099995328942" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="27.709999474506" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="27.709999474506" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="17.7099996691334" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="18.7099996496707" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="15.7099997080589" hidden="0" customWidth="1"/>
-    <col min="12" max="12" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="11.2056266178838" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="15.8703495591654" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14.704168823845" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="15.8703495591654" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20.5350725004471" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="15.8703495591654" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="17.0365302944859" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="21.7012532357675" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="21.7012532357675" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="22.867433971088" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="31.0306991183309" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="32.1968798536513" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="36.861602794933" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="38.0277835302534" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,233 +464,167 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46193</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>-6.54521503982531</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>122.144768855906</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1.37763603389116</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>3.64805238445069</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>-5.0179405975465</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>141.561250674538</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>-2.47355109301419</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>124.91975147844</v>
+        <v>46200</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F2" t="n">
+        <v>59.34</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I2" t="n">
+        <v>58.15</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="P2" t="n">
+        <v>59.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46193</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-3.38679405675504</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>61.4911909852218</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1.47357365786164</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>3.11160393615509</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>-2.59651230548018</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>71.2660065827618</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>-1.27992863334923</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>62.8881970790661</v>
+        <v>46200</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I3" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P3" t="n">
+        <v>29.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46193</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>-1.42646852936583</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>31.1047624139066</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1.59617862520319</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>2.677349636041</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>-1.09361331920705</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>36.0492644137834</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>-0.539087374286999</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>31.811425302421</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="s">
+        <v>46200</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>1.70571747299372</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>120.946782657062</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>2.28398103173424</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>1.77882770483714</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>1.80168531121341</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>141.618729679532</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.300832194863246</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>124.664602059234</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.88261634872008</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>60.888090264325</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>2.21291634756307</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>1.82445916572</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0.932274503898239</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>71.2949431676588</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.155664356853676</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>62.7597475202918</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>46194</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.371745203237798</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>30.7996893727997</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>2.14361744587973</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>1.87441827999637</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0.392660497879563</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>36.0639017233536</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>0.0655635691083302</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>31.7464502556895</v>
+      <c r="E4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F4" t="n">
+        <v>117.88</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I4" t="n">
+        <v>115.51</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P4" t="n">
+        <v>117.49</v>
       </c>
     </row>
   </sheetData>

--- a/files/SSN_upcoming_projections.xlsx
+++ b/files/SSN_upcoming_projections.xlsx
@@ -65,10 +65,10 @@
     <t xml:space="preserve">1H</t>
   </si>
   <si>
+    <t xml:space="preserve">Adelaide Thunderbirds</t>
+  </si>
+  <si>
     <t xml:space="preserve">Melbourne Vixens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Coast Fever</t>
   </si>
   <si>
     <t xml:space="preserve">1Q</t>
@@ -411,7 +411,7 @@
   <cols>
     <col min="1" max="1" width="11.2056266178838" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="15.8703495591654" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="16.7099996885961" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="21.7099995912824" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="16.7099996885961" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="14.704168823845" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="15.8703495591654" hidden="0" customWidth="1"/>
@@ -479,7 +479,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
@@ -491,45 +491,45 @@
         <v>18</v>
       </c>
       <c r="E2" t="n">
-        <v>0.35</v>
+        <v>-5.36</v>
       </c>
       <c r="F2" t="n">
-        <v>59.34</v>
+        <v>52.78</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="H2" t="n">
-        <v>0.35</v>
+        <v>-5.48</v>
       </c>
       <c r="I2" t="n">
-        <v>58.15</v>
+        <v>54.39</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.86</v>
+        <v>1.06</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="M2" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.19</v>
+        <v>0.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0.59</v>
+        <v>-5.18</v>
       </c>
       <c r="P2" t="n">
-        <v>59.15</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -541,45 +541,45 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>0.14</v>
+        <v>-2.25</v>
       </c>
       <c r="F3" t="n">
-        <v>30.02</v>
+        <v>26.7</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="H3" t="n">
-        <v>0.15</v>
+        <v>-2.3</v>
       </c>
       <c r="I3" t="n">
-        <v>29.42</v>
+        <v>27.51</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.86</v>
+        <v>1.06</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="M3" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1</v>
+        <v>0.13</v>
       </c>
       <c r="O3" t="n">
-        <v>0.27</v>
+        <v>-2.16</v>
       </c>
       <c r="P3" t="n">
-        <v>29.92</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46200</v>
+        <v>46207</v>
       </c>
       <c r="B4" t="s">
         <v>20</v>
@@ -591,40 +591,40 @@
         <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>0.67</v>
+        <v>-10.38</v>
       </c>
       <c r="F4" t="n">
-        <v>117.88</v>
+        <v>104.85</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="H4" t="n">
-        <v>0.68</v>
+        <v>-10.62</v>
       </c>
       <c r="I4" t="n">
-        <v>115.51</v>
+        <v>108.04</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.86</v>
+        <v>1.06</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>1.07</v>
       </c>
       <c r="M4" t="n">
-        <v>0.48</v>
+        <v>0.36</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.38</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.15</v>
+        <v>-10.02</v>
       </c>
       <c r="P4" t="n">
-        <v>117.49</v>
+        <v>105.35</v>
       </c>
     </row>
   </sheetData>
